--- a/tools/reading-season.xlsx
+++ b/tools/reading-season.xlsx
@@ -516,7 +516,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>Open the Applications tab, click cell A2, then File → Import → Upload the applications CSV → 'Replace data at selected cell'.</t>
+          <t>Open the Applications tab, click cell A1 (the header row — the CSV brings its own), then File → Import → Upload the applications CSV → 'Replace data at selected cell'. The first applicant must land in row 2; if you ever see two header rows, delete the extra one.</t>
         </is>
       </c>
     </row>
